--- a/csv Source/Test Directory/01_items.xlsx
+++ b/csv Source/Test Directory/01_items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Release\CSV-Toolkit\csv Source\Test Directory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BC6BF6-A3E7-4ECB-98AD-60C397B2327F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9981DAB4-C98D-40E3-961E-E2D11B0F09BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="419">
-  <si>
-    <t>{ItemID/int/PK}</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="421">
+  <si>
+    <t>{ItemID/int}</t>
   </si>
   <si>
     <t>{ItemName/string/UNIQUE}</t>
@@ -37,7 +37,7 @@
     <t>{Level/int/CHECK(VALUE &gt;= 0 AND VALUE &lt;= 100)}</t>
   </si>
   <si>
-    <t>{ShopPrice/float/PK/CHECK IN(3.14|1.71)}</t>
+    <t>{ShopPrice/float/CHECK IN(3.14|1.71)}</t>
   </si>
   <si>
     <t>{SellPrice/float/CHECK NOT IN(3.14|1.71)}</t>
@@ -49,7 +49,7 @@
     <t>{DisplayText/string/NOT NULL}</t>
   </si>
   <si>
-    <t>{AssetPath/AssetId/REF}</t>
+    <t>{AssetPath/AssetId}</t>
   </si>
   <si>
     <t>{Internal_Name/string/UNIQUE}</t>
@@ -1277,6 +1277,14 @@
   </si>
   <si>
     <t>item_100</t>
+  </si>
+  <si>
+    <t>숫자가 둘이지요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자는 3개 아님?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1757,7 +1765,7 @@
         <v>300</v>
       </c>
       <c r="G3">
-        <v>150</v>
+        <v>3.14</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -1779,9 +1787,6 @@
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1796,8 @@
       <c r="F4">
         <v>400</v>
       </c>
-      <c r="G4">
-        <v>200</v>
+      <c r="G4" t="s">
+        <v>419</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -1821,13 +1826,13 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F5">
         <v>500</v>
       </c>
       <c r="G5">
-        <v>250</v>
+        <v>1.71</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -1861,8 +1866,8 @@
       <c r="F6">
         <v>600</v>
       </c>
-      <c r="G6">
-        <v>300</v>
+      <c r="G6" t="s">
+        <v>420</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -5205,5 +5210,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>